--- a/data/trans_orig/IP07_A12_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07_A12_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de estar demasiado cansado/a para disfrutar de las cosas que le gustan, percibida por el adulto en 2023 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según la frecuencia de estar demasiado cansado/a para disfrutar de las cosas que le gustan, percibida por el/la adulto/a en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,16%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2564</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4106</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4455</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4659</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>19,35%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5728</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4538</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5753</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8805</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4921</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13954</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>45,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6068</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3050</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9957</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21,82%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35,81%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16757</t>
+          <t>9429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16389</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23524</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20442</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15418</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>24540</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18017</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13622</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22065</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>64,8%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>48,99%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>79,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>24124</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28734</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>42140</t>
+          <t>35309</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34958</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49074</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>73,67%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>30968</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>30968</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>30968</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>27805</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>27805</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>27805</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>64232</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>64232</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64232</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,107 +1402,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8638</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1774</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8909</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7871</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1774</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>8950</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -1515,107 +1515,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1096</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4444</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4423</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>4280</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1096</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>4457</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1942</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8965</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,21%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5326</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11653</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14648</t>
+          <t>14001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25919</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18052</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36425</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>53,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11968</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23233</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28114</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39689</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>40082</t>
+          <t>35459</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>25397</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58300</t>
+          <t>48113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38336</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27976</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>46734</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>56,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>59346</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>46115</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>72265</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>76,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40274</t>
+          <t>35931</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>29113</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49422</t>
+          <t>41261</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>99621</t>
+          <t>74266</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81395</t>
+          <t>61576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>122016</t>
+          <t>85865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>67851</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>67851</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>67851</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77736</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77736</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77736</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>150055</t>
+          <t>119993</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>150055</t>
+          <t>119993</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>150055</t>
+          <t>119993</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1356</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4722</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2188</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5574</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,18%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -2197,107 +2197,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3108</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2669</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3631</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4076</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2457</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5563</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1669</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4589</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>7002</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>3677</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>11486</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>22,84%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>37,46%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8610</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>13568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -2536,74 +2536,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>29985</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>26318</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>32674</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>75,32%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>19017</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>14418</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>23154</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>62,02%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>47,02%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>19040</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>14978</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>23118</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>62,19%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>48,93%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>75,51%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>33029</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>28159</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>36125</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>85,52%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>72,91%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>93,53%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>79</t>
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>52045</t>
+          <t>49025</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45389</t>
+          <t>43365</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57299</t>
+          <t>54084</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>34942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>34942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>34942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>30663</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>30663</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>30663</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38623</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38623</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38623</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>69285</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>69285</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69285</t>
+          <t>65556</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8109</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>6603</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3053</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11673</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>6946</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3248</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>12094</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>16,86%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>29,8%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7725</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16025</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2802</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>8137</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>20,77%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>353</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>426</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4965</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>11929</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>5427</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2087</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>11668</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>29,78%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12793</t>
+          <t>11847</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>39895</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>31830</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>45540</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>80,47%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>64,21%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>91,86%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>21628</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>16074</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>27095</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>55,2%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>41,03%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>69,16%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>42545</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34583</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48736</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>64172</t>
+          <t>62360</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52337</t>
+          <t>51176</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>74530</t>
+          <t>71739</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>49575</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>49575</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>49575</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>39177</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>39177</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>39177</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>41189</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>41189</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>41189</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>90764</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>90764</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>90764</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,107 +3448,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1586</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>16,26%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>3906</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>15,55%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>423</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3959</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2541</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1124</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3901</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>538</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -3674,107 +3674,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>3935</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>9386</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>15,39%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>36,72%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>3777</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>1244</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>8623</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>34,33%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>7097</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>3916</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>27,76%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>7686</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>4801</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>11023</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>40,76%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>25,46%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>58,45%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10746</t>
+          <t>11525</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>20360</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>11790</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>7832</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>15693</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>46,13%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>30,64%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>61,4%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>10603</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>7177</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>13519</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>56,22%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>38,06%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>71,69%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15576</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>22367</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17254</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>18859</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>18859</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>18859</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4243,107 +4243,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>2480</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>3159</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>3671</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>560</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>535</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>619</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>22473</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>19581</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>23602</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>81,38%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>22423</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>19899</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>23533</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>93,27%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>82,77%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>23382</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22077</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>24609</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>47133</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>43984</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>48012</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>24062</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>24062</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>24062</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>24042</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>25192</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>49253</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>49253</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>49253</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>3838</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>1462</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>8499</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>1876</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>6761</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>1841</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>5996</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>349</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>6364</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2637</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>11430</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>3591</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>7664</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>28020</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>31296</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>13100</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>6814</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>26393</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>30,27%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>6747</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>3398</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>12553</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>12004</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>32561</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>57733</t>
+          <t>65860</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>51369</t>
+          <t>54512</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>63039</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>70069</t>
+          <t>58518</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>53448</t>
+          <t>51485</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>80085</t>
+          <t>64319</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>127802</t>
+          <t>124378</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>110833</t>
+          <t>110370</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>138742</t>
+          <t>134001</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>87200</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>87200</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>87200</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>72301</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>72301</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>72301</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>95597</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>167898</t>
+          <t>161139</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>167898</t>
+          <t>161139</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>167898</t>
+          <t>161139</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>9150</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>1790</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>6236</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>6418</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>3384</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>7948</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -5720,72 +5720,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>6065</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2271</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>11938</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>6,08%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>1163</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>5377</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>6421</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>5509</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>11893</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -5833,72 +5833,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14773</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>8565</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>22199</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>22,24%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>12592</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>7557</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>18985</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>9,62%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>24,16%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>20659</t>
+          <t>21590</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>28517</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>19778</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>34634</t>
+          <t>38454</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -5946,72 +5946,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>73409</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>63902</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>81166</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>73,54%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>64,01%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>81,31%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>61698</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>54466</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>67579</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>78,53%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>69,32%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>68877</t>
+          <t>69676</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>61224</t>
+          <t>61504</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>77189</t>
+          <t>75642</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,17 +6021,17 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>130575</t>
+          <t>143085</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>120013</t>
+          <t>131142</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>140362</t>
+          <t>154430</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>99825</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>99825</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>99825</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>78569</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>78569</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>78569</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>93106</t>
+          <t>88303</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>93106</t>
+          <t>88303</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>93106</t>
+          <t>88303</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>171675</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>171675</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>171675</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11270</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>5845</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>19657</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>14977</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>9075</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>23044</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>17479</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>35125</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>2555</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>11959</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>3486</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>13845</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>13811</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>23637</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>15174</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>33778</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>18326</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>11385</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>26668</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>49434</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>34783</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>68958</t>
+          <t>57482</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>76865</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>61815</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>97418</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>58055</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>43418</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>72831</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>79250</t>
+          <t>57670</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>63174</t>
+          <t>46454</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>101345</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>137305</t>
+          <t>134535</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>115800</t>
+          <t>114712</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>163058</t>
+          <t>156284</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>302191</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>278960</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>319865</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>71,95%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>66,42%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>76,16%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>270465</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>253007</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>295159</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>73,27%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>68,54%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>315390</t>
+          <t>255180</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>289031</t>
+          <t>240268</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>336001</t>
+          <t>269836</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>585855</t>
+          <t>557371</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>555292</t>
+          <t>533483</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>615138</t>
+          <t>581580</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
